--- a/tests/FatEq_C_x_13M_D5_0004.xlsx
+++ b/tests/FatEq_C_x_13M_D5_0004.xlsx
@@ -533,10 +533,10 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="F2" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="G2" t="n">
         <v>9</v>
@@ -575,11 +575,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[16,20,13,27,26,21,23,24,25,29,10,12,14,22]</t>
+          <t>[16,20,13,27,26,21,23,24,25,29,10,17,12,14,22]</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -600,10 +600,10 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>16.47</v>
+        <v>16.77</v>
       </c>
       <c r="F3" t="n">
-        <v>18.47</v>
+        <v>18.77</v>
       </c>
       <c r="G3" t="n">
         <v>7</v>
@@ -642,11 +642,11 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[16,15,26,25,19,18,17,12,14,11,28,22,36]</t>
+          <t>[16,15,26,21,23,25,19,18,10,17,12,14,11,28,22,36]</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -667,10 +667,10 @@
         <v>46</v>
       </c>
       <c r="E4" t="n">
-        <v>15.1</v>
+        <v>15.43</v>
       </c>
       <c r="F4" t="n">
-        <v>61.1</v>
+        <v>61.43</v>
       </c>
       <c r="G4" t="n">
         <v>64</v>
@@ -734,10 +734,10 @@
         <v>46</v>
       </c>
       <c r="E5" t="n">
-        <v>7.600000000000001</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>53.6</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
         <v>50</v>
@@ -776,11 +776,11 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[77,71,69,78]</t>
+          <t>[77,71,69,78,48]</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -801,10 +801,10 @@
         <v>196</v>
       </c>
       <c r="E6" t="n">
-        <v>15.69999999999999</v>
+        <v>16.03</v>
       </c>
       <c r="F6" t="n">
-        <v>211.7</v>
+        <v>212.03</v>
       </c>
       <c r="G6" t="n">
         <v>243</v>
@@ -843,11 +843,11 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[215,220,217,222,225,232,231,238,236,245,261,262]</t>
+          <t>[189,219,215,220,217,222,225,231,238,236,245,261,262]</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -868,10 +868,10 @@
         <v>196</v>
       </c>
       <c r="E7" t="n">
-        <v>31.66999999999999</v>
+        <v>31.90000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>227.67</v>
+        <v>227.9</v>
       </c>
       <c r="G7" t="n">
         <v>282</v>
@@ -910,11 +910,11 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[179,215,193,216,217,218,232,235,237,238,253,256,257,259,262]</t>
+          <t>[186,179,219,215,193,216,217,218,232,235,237,238,253,256,257,259,262]</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -935,10 +935,10 @@
         <v>355</v>
       </c>
       <c r="E8" t="n">
-        <v>5.800000000000011</v>
+        <v>6.399999999999977</v>
       </c>
       <c r="F8" t="n">
-        <v>360.8</v>
+        <v>361.4</v>
       </c>
       <c r="G8" t="n">
         <v>331</v>
@@ -977,11 +977,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[355,402]</t>
+          <t>[346,402,355]</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -995,28 +995,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sem veículos válidos</t>
+          <t>Fluxo interrompido por algum evento</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>355</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>6.569999999999993</v>
       </c>
       <c r="F9" t="n">
-        <v>355</v>
+        <v>361.57</v>
       </c>
       <c r="G9" t="n">
-        <v>-1</v>
+        <v>341</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[341]</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1044,11 +1044,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[351,402,355,390]</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
